--- a/data/UK-BDI-2025-insects-wider-countryside.xlsx
+++ b/data/UK-BDI-2025-insects-wider-countryside.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Prog710-NCPA\0827 Publication of UKBIs\OFFICIAL-SENSITIVE\BIYP2025\datasheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\balint.szilagyi\york_msc\aai_summative\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{244E3ABE-25CA-4E98-A3A9-E7C3EDA8E783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" xr2:uid="{ED6C98B2-EC21-46E3-ADD4-F8B59E8632CC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{ED6C98B2-EC21-46E3-ADD4-F8B59E8632CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover_sheet" sheetId="1" r:id="rId1"/>
@@ -2828,6 +2828,9 @@
   </hyperlinks>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 CLASSIFICATION: CONFIDENTIAL - COMMERCIAL IN CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2919,6 +2922,9 @@
   </hyperlinks>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 CLASSIFICATION: CONFIDENTIAL - COMMERCIAL IN CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -3017,6 +3023,9 @@
   </sheetData>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 CLASSIFICATION: CONFIDENTIAL - COMMERCIAL IN CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -9650,6 +9659,9 @@
   </sheetData>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 CLASSIFICATION: CONFIDENTIAL - COMMERCIAL IN CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <tableParts count="7">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
@@ -10398,6 +10410,9 @@
   </sheetData>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 CLASSIFICATION: CONFIDENTIAL - COMMERCIAL IN CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <tableParts count="7">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
@@ -13913,6 +13928,9 @@
   </sheetData>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 CLASSIFICATION: CONFIDENTIAL - COMMERCIAL IN CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <tableParts count="3">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
@@ -13923,6 +13941,11 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="d1117845-93f6-4da3-abaa-fcb4fa669c78" ContentTypeId="0x010100A5BF1C78D9F64B679A5EBDE1C6598EBC01" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
@@ -13930,12 +13953,72 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="d1117845-93f6-4da3-abaa-fcb4fa669c78" ContentTypeId="0x010100A5BF1C78D9F64B679A5EBDE1C6598EBC01" PreviousValue="false"/>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <cf401361b24e474cb011be6eb76c0e76 xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Crown</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">69589897-2828-4761-976e-717fd8e631c9</TermId>
+        </TermInfo>
+      </Terms>
+    </cf401361b24e474cb011be6eb76c0e76>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <k85d23755b3a46b5a51451cf336b2e9b xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </k85d23755b3a46b5a51451cf336b2e9b>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="63fb2e78-87de-42f7-8d79-90c3117f9953">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Topic xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">Indicators</Topic>
+    <HOMigrated xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">false</HOMigrated>
+    <ddeb1fd0a9ad4436a96525d34737dc44 xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">External</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">1104eb68-55d8-494f-b6ba-c5473579de73</TermId>
+        </TermInfo>
+      </Terms>
+    </ddeb1fd0a9ad4436a96525d34737dc44>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lae2bfa7b6474897ab4a53f76ea236c7 xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Official</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">14c80daa-741b-422c-9722-f71693c9ede4</TermId>
+        </TermInfo>
+      </Terms>
+    </lae2bfa7b6474897ab4a53f76ea236c7>
+    <TaxCatchAll xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">
+      <Value>6</Value>
+      <Value>10</Value>
+      <Value>9</Value>
+      <Value>8</Value>
+      <Value>7</Value>
+    </TaxCatchAll>
+    <fe59e9859d6a491389c5b03567f5dda5 xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Core Defra</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">026223dd-2e56-4615-868d-7c5bfd566810</TermId>
+        </TermInfo>
+      </Terms>
+    </fe59e9859d6a491389c5b03567f5dda5>
+    <Team xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">Environment Science and Analysis</Team>
+    <n7493b4506bf40e28c373b1e51a33445 xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Work Delivery</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">388f4f80-46e6-4bcd-8bd1-cea0059da8bd</TermId>
+        </TermInfo>
+      </Terms>
+    </n7493b4506bf40e28c373b1e51a33445>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Defra document" ma:contentTypeID="0x010100A5BF1C78D9F64B679A5EBDE1C6598EBC0100F8D2F4F0C14EEF489D81A6495532A706" ma:contentTypeVersion="39" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cde751e99fe92162a2da6a5bc4d55823">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="662745e8-e224-48e8-a2e3-254862b8c2f5" xmlns:ns3="63fb2e78-87de-42f7-8d79-90c3117f9953" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1b3c43ef39c891674f6058a9f4a1699a" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -14231,72 +14314,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <cf401361b24e474cb011be6eb76c0e76 xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Crown</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">69589897-2828-4761-976e-717fd8e631c9</TermId>
-        </TermInfo>
-      </Terms>
-    </cf401361b24e474cb011be6eb76c0e76>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <k85d23755b3a46b5a51451cf336b2e9b xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </k85d23755b3a46b5a51451cf336b2e9b>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="63fb2e78-87de-42f7-8d79-90c3117f9953">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Topic xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">Indicators</Topic>
-    <HOMigrated xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">false</HOMigrated>
-    <ddeb1fd0a9ad4436a96525d34737dc44 xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">External</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">1104eb68-55d8-494f-b6ba-c5473579de73</TermId>
-        </TermInfo>
-      </Terms>
-    </ddeb1fd0a9ad4436a96525d34737dc44>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lae2bfa7b6474897ab4a53f76ea236c7 xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Official</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">14c80daa-741b-422c-9722-f71693c9ede4</TermId>
-        </TermInfo>
-      </Terms>
-    </lae2bfa7b6474897ab4a53f76ea236c7>
-    <TaxCatchAll xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">
-      <Value>6</Value>
-      <Value>10</Value>
-      <Value>9</Value>
-      <Value>8</Value>
-      <Value>7</Value>
-    </TaxCatchAll>
-    <fe59e9859d6a491389c5b03567f5dda5 xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Core Defra</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">026223dd-2e56-4615-868d-7c5bfd566810</TermId>
-        </TermInfo>
-      </Terms>
-    </fe59e9859d6a491389c5b03567f5dda5>
-    <Team xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">Environment Science and Analysis</Team>
-    <n7493b4506bf40e28c373b1e51a33445 xmlns="662745e8-e224-48e8-a2e3-254862b8c2f5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Work Delivery</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">388f4f80-46e6-4bcd-8bd1-cea0059da8bd</TermId>
-        </TermInfo>
-      </Terms>
-    </n7493b4506bf40e28c373b1e51a33445>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4E294AB-C604-4332-B738-58469C7D03CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{367A8B5B-8BC4-401F-B132-9F4AD02F9F0D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -14304,15 +14330,19 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4E294AB-C604-4332-B738-58469C7D03CB}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10ECD052-97F5-4043-9FF8-66E0FF937B1D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="662745e8-e224-48e8-a2e3-254862b8c2f5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="63fb2e78-87de-42f7-8d79-90c3117f9953"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3E6383B-E8F9-46E3-9C99-9B858AFF3DEA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14330,16 +14360,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10ECD052-97F5-4043-9FF8-66E0FF937B1D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="662745e8-e224-48e8-a2e3-254862b8c2f5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="63fb2e78-87de-42f7-8d79-90c3117f9953"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>